--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20261015.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20261015.xlsx
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>10,112,000</t>
+          <t>8,553,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1019,17 +1019,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>8,553,000</t>
+          <t>10,112,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>致伸</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>1,196,000</t>
+          <t>18,481,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>致伸</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>18,481,000</t>
+          <t>1,196,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>三陽工業</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>17,752,000</t>
+          <t>56,668,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>三陽工業</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>56,668,000</t>
+          <t>17,752,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
